--- a/resources/tenable/TenableWAS_bWAPP.xlsx
+++ b/resources/tenable/TenableWAS_bWAPP.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,31 +487,6 @@
           <t>instances</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>detection_method</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>detection_result</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>insight</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>log_method</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>product_detection_result</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,9 +519,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -575,31 +547,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/portal.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Technology PHP version 5.5.9 has been detected. Upgrade to the last supported version of PHP: 8.1', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -632,9 +579,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -663,31 +607,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.41 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -720,9 +639,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -751,31 +667,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.26 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -808,9 +699,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -839,31 +727,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.27 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -896,9 +759,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -927,31 +787,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.33 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -984,9 +819,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1015,31 +847,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.48 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1072,9 +879,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1103,31 +907,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.49 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1160,9 +939,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1191,31 +967,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.52 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1248,9 +999,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1279,31 +1027,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.53 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1336,9 +1059,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1367,31 +1087,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.54 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1424,9 +1119,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1455,31 +1147,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.55 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1512,9 +1179,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1543,31 +1207,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.56 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1600,9 +1239,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1631,31 +1267,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.60 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1688,9 +1299,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1719,31 +1327,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.39 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1776,9 +1359,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1807,31 +1387,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.38 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1864,9 +1419,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1895,31 +1447,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.9 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1952,9 +1479,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1983,31 +1507,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.10 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2040,9 +1539,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2071,31 +1567,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.12 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2128,9 +1599,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2159,31 +1627,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.16 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2216,9 +1659,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2247,31 +1687,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.25 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2304,9 +1719,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2335,31 +1747,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.28 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2392,9 +1779,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2423,31 +1807,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.34 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2480,9 +1839,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2511,31 +1867,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.58 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2568,9 +1899,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2599,31 +1927,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.59 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2656,9 +1959,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2687,31 +1987,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.62 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2744,9 +2019,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2775,31 +2047,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/apps/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/stylesheets/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/documents/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/images/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/phpinfo.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/js/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/.', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/login.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/training_install.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/db/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/install.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/info_install.php.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/#/.', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/portal.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/portal.php.', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner did not find any Strict-Transport-Security header in the response returned by the target when querying URL https://juice-shop-388277804329.us-west1.run.app/apps/movie_search.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2832,9 +2079,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2863,31 +2107,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/passwords/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/documents/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/db/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/js/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/soap/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/images/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'WAS Scanner has enumerated the following Directory Listings: - https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2920,9 +2139,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2951,31 +2167,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;!DOCTYPE html PUBLIC "-//W3C//DTD XHTML 1.0 Transitional//EN" "DTD/xhtml1-transitional.dtd"&gt; &lt;html xmlns="http://www.w3.org/1999/xhtml"&gt;&lt;head&gt; &lt;style type="text/css"&gt; body {background-color: #ffffff; color: #000000;}', 'output': 'The scanner detected the presence of the `phpinfo.php` file on https://juice-shop-388277804329.us-west1.run.app/phpinfo. php', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3008,9 +2199,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3039,31 +2227,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;?xml version="1.0"?&gt; &lt;configuration&gt; &lt;configSections&gt; &lt;sectionGroup name="system.web.extensions" type="System.Web.Configuration.SystemWebExtensionsSectionGroup, System.Web. Extensions, Version=3.5.0.0, Culture=neutral, PublicKeyToken=31BF3856AD364E35"&gt;', 'output': 'The scanner detected the presence of the `web.config` file on https://juice-shop-388277804329.us-west1.run.app/passwords /web.config', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}]</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3096,9 +2259,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3127,31 +2287,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength -------------------------------------------------------------------- TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3184,9 +2319,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3215,31 +2347,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?php', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'The following patterns were detected in the HTTP response body : - &lt;?', 'output': "The scanner detected the presence of a 'PHP' source code in the web application response.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3271,10 +2378,6 @@
           <t>['CWE 20', 'CWE 400', 'WASC Denial of Service', 'WASC Improper Input Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2018-11763', 'BID 105414']</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3303,31 +2406,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.35 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3360,9 +2438,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3391,31 +2466,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Current Version: 2.4.7 Fixed Version: 2.4.43 Detected technology URL: https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3449,9 +2499,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3478,31 +2525,6 @@
       <c r="N35" t="inlineStr">
         <is>
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;?xml version="1.0"?&gt; &lt;configuration&gt; &lt;configSections&gt; &lt;sectionGroup name="system.web.extensions" type="System.Web.Configuration.SystemWebExtensionsSectionGroup, System.Web. Extensions, Version=3.5.0.0, Culture=neutral, PublicKeyToken=31BF3856AD364E35"&gt;', 'output': 'The scanner detected the presence of the `web.config` file on https://juice-shop-388277804329.us-west1.run.app/passwords /web.config', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}]</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -3543,9 +2565,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3574,31 +2593,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/stylesheets/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak has no X-Frame-Options header defined', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak has no X-Frame-Options header defined', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/images/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/install.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/db/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/js/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/info_install.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/user_new.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/training_install.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/info.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php has no X-Frame-Options header defined', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/apps/movie_search has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/phpinfo.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/training.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/login.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/documents/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Page https://juice-shop-388277804329.us-west1.run.app/apps/ has no X-Frame-Options header defined', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3636,9 +2630,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3667,31 +2658,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': '', 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript which prevents the HTTPOnly attribute from being used. If the cookie is set to handle sensitive information (for example session-based information), it should be set via the HTTP method.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3728,9 +2694,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3759,31 +2722,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': '', 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript without the Secure flag set.", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3816,9 +2754,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3847,31 +2782,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'payload': '', 'proof': '', 'output': 'The following form has been found to have not restricted \'password auto complete\' attribute : &lt;form action="/user_new.php" method="POST"&gt; &lt;input type="text" id="login" name="login"&gt; &lt;/input&gt; &lt;input type="text" id="email" name="email" size="30"&gt; &lt;/input&gt; &lt;input type="password" id="password" name="password"&gt; &lt;/input&gt; &lt;input type="password" id="password_conf" name="password_conf"&gt; &lt;/input&gt; &lt;input type="text" id="secret" name="secret" size="40"&gt; &lt;/input&gt; &lt;input type="checkbox" id="mail_activation" name="mail_activation" value=""&gt; &lt;/input&gt; &lt;button type="submit" name="action" value="create"&gt; Create &lt;/button&gt; &lt;/form&gt;', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3904,9 +2814,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3935,31 +2842,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /stylesheets/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/apps /movie_search: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /class.nusoap_base.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/web.config.bak: - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /class.soap_fault.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/db/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /install.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /images/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/#/: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /info_install.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /phpinfo.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/portal.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /portal.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /documents/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /soap/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /nusoap.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /apps/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /training_install.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/soap /class.wsdlcache.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/heroes.xml: - Server: Google Frontend', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/db /bwapp.sqlite: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app/js/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/: - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /login.php: - X-Powered-By: PHP/5.5.9-1ubuntu4.14 - Server: Google Frontend', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following header information disclosures have been detected on https://juice-shop-388277804329.us-west1.run.app /passwords/wp-config.bak: - Server: Google Frontend', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}]</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3992,9 +2874,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4023,31 +2902,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of a correct X-Content-Type-Options header configuration in the target application response', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4080,9 +2934,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4111,31 +2962,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4168,9 +2994,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4199,31 +3022,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/images/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php has no Content Security Policy defined.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/install.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/documents/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/login.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/js/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/ has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php has no Content Security Policy defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4256,9 +3054,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4287,31 +3082,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml has no Cache Control header defined.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/login.php has invalid directive found : - post-check=0 https://juice-shop-388277804329.us-west1.run.app/login.php has invalid directive found : - pre-check=0', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak has no Cache Control header defined.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/documents/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/install.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/images/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/js/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php has no Cache Control header defined.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/db/ has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak has no Cache Control header defined.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/training.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php has no Cache Control header defined.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4344,9 +3114,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4375,31 +3142,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '&lt;form action="/login.php" method="POST"&gt; &lt;input type="text" id="login" name="login" size="20" autocomplete="off"&gt; &lt;/input&gt; &lt;input type="password" id="password" name="password" size="20" autocomplete="off"&gt; &lt;/input&gt; &lt;select name="security_level"&gt; &lt;option value="0"&gt; low &lt;/option&gt; &lt;option value="1"&gt; medium &lt;/option&gt; &lt;option value="2"&gt; high &lt;/option&gt; &lt;/select&gt; &lt;button type="submit" name="form" value="submit"&gt; Login &lt;/button&gt; &lt;/form&gt;', 'output': 'No anti-CSRF token could have been found in the login form attached in proof. By requesting it several times, the scanner could not find any dynamic input field that would generate a token used by the application to confirm the user intention to submit this form.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4432,9 +3174,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4463,31 +3202,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': '', 'proof': 'PHPSESSID=711vt1tpgrucudl1kaq9t074f5; Path=/', 'output': "The scanner detected a cookie named 'PHPSESSID' set with JavaScript which does not have the 'SameSite' attribute set.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4510,15 +3224,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4545,31 +3255,6 @@
       <c r="N47" t="inlineStr">
         <is>
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Engine Version 2.26.10-1603 Plugins Version 202411140727 Scan ID 45c6aad7-0097-4f4e-a4bc-4623af2d119b Start Time 2024-11-19 00:10:32 +0000 Duration 09:35:35 Requests 706972 Crawler Requests 92 Requests/s 24.7968 Mean Response Time 0.1317s Bandwidth Usage - Data to Target 274 MB - Data from Target 2.24 GB Timeouts Encountered Network Timeouts 7 Browser Timeouts 0 Browser Respawns 0 HTTP Protocols Detected - HTTPs Authentication Identified - None Plugins - 729 have been included per scan policy - 792 have been started based on target information collected List of plugins is available in 'plugins.csv' attachment. Settings used to conduct this scan are available in 'configuration.csv' attachment.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -4613,15 +3298,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4650,31 +3331,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scan has discovered 173 distinct URLs. The following is a breakdown of which URLs were audited: - 69 effectively audited - 8 not audited due to the page was too similar to another page already audited - 42 not queued due to file extension exclusions - 29 not queued due to the URL not being in the target domain - 24 not queued due to the URL being considered redundant with other processed URLs - 1 not queued due to the URL containing a fragment which is a feature of browsers and not included in HTTP requests. The page being referred to by the fragment shall still be audited by the scanner. For URLs we received responses for, here is a distribution of the content type headers: - 1 application/javascript - 2 application/x-trash - 1 application/xml - 7 image/gif - 4 image/jpeg - 11 image/png - 1 text/css - 26 text/html - 48 text/html;charset=utf-8 Response times ranged between 0.020808s and 0.281579s. You can access the complete list of URLs with the information collected by the scan as an attachment to this plugin.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4697,15 +3353,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4734,31 +3386,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner encountered 7 network timeouts during the scan. See the attachment for more details', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4781,15 +3408,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4818,31 +3441,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/login.php', 'payload': '', 'proof': '', 'output': "Potential login form has been identified in URL 'https://juice-shop-388277804329.us-west1.run.app/login.php' with following fields: - login (TEXT) - password (PASSWORD) - No name or id (SELECT) - form (SUBMIT) To perform authenticated scan, configure your scan and add 'Login Form' authentication, with the URL associated to this plugin and as login parameters values for the above non-hidden fields.", 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4865,15 +3463,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4902,31 +3496,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner was able to identify several HTTP methods that can be used for one or several URLs. The results are available as attachments.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4949,15 +3518,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4986,31 +3551,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /js/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https%3A%2F%2Fjuice-shop-388277804329.us-west1.run.app%2Fapps%2Fsetup%2Fsetup-s%2F%25u002e%25u002e%', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 400', 'output': "A response has been received with a response code '400' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /apps/setup/setup-s/%u002e%u002e/%u002e%u002e/log.jsp'.", 'request_method': 'GET', 'http_status_code': 400, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 405', 'output': "A response has been received with a response code '405' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP TRACE request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/#/'.", 'request_method': 'TRACE', 'http_status_code': 405, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /db/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /stylesheets/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 406', 'output': "A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/heroes'.", 'request_method': 'GET', 'http_status_code': 406, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /images/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /soap/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /documents/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /apps/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/was-tnb.aspx', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 502', 'output': "A response has been received with a response code '502' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP DEBUG request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/apps/was-tnb.aspx'.", 'request_method': 'DEBUG', 'http_status_code': 502, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /documents/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /stylesheets/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 406', 'output': "A response has been received with a response code '406' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /passwords/web.config'.", 'request_method': 'GET', 'http_status_code': 406, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /apps/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /images/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /soap/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /js/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/.htaccess', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /db/.htaccess'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/server-status', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /server-status'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/.htpasswd', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 403', 'output': "A response has been received with a response code '403' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run. app/.htpasswd'.", 'request_method': 'GET', 'http_status_code': 403, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php?cb=was_302_ebiu', 'input_type': '', 'input_name': '', 'payload': '', 'proof': 'HTTP/2 400', 'output': "A response has been received with a response code '400' which may require further investigation to verify if this response is due to an abnormal behavior of the target. The response has been triggered by an HTTP GET request made on the URL 'https://juice-shop-388277804329.us-west1.run.app /install.php'.", 'request_method': 'GET', 'http_status_code': 400, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5033,15 +3573,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5070,31 +3606,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The framework has detected the following technologies in the target application: - PHP (v5.5.9) - Apache (v2.4.7)', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5117,15 +3628,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5154,31 +3661,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The following cookies have been collected during the scan of the target: - 0 cookie(s) specified via Set-Cookie - 1 cookie(s) set via JavaScript code The complete list of the cookies is available in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5201,15 +3683,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5238,31 +3716,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common file 'install.php' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5285,15 +3738,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5322,31 +3771,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'db' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'documents' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'images' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'stylesheets' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'apps' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'soap' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'js' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "The common directory 'passwords' was identified by the scanner.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5369,15 +3793,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5406,31 +3826,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Private IP Addresses Collected: 3 Listed below are each private ip address: 169.254.169.1 found on 1 URL 169.254.169.126 found on 1 URL 127.0.0.1 found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5453,15 +3848,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5490,31 +3881,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Number of Email Addresses Collected: 3 Listed below are each email address and the number of URLs where the email address has been found: license@php.net found on 1 URL bee6885858486f31043e5839c735d99457f045affd0bwapp-bee@mailinator.comA found on 1 URL A.I.M.6885858486f31043e5839c735d99457f045affd0bwapp-aim@mailinator.comA found on 1 URL', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5537,15 +3903,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5574,31 +3936,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "Access to URL 'https://juice-shop-388277804329.us-west1.run.app/#/' has been confirmed. Target Information ------------------------ Domain Name : juice-shop-388277804329.us-west1.run.app IP Address : 216.239.32.53 Response Information --------------------------- Status Code : 302 Return Code : ok Return Message: No error Response Time : 0.078037s Response Size : 294 bytes Content-Type : text/html DEBUG INFORMATION ----------------------- HTTP Network Timeout : 30s", 'request_method': 'GET', 'http_status_code': 302, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5621,15 +3958,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5658,31 +3991,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "WAS Scanner has taken a screenshot of the page at url 'https://juice-shop-388277804329.us-west1.run.app/#/' with dimensions 1600x1200. Please see the attachment for the screenshot image.", 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5705,15 +4013,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5742,31 +4046,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/login.php', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-388277804329.us-west1.run.app/login. php with input fields : - login (text) - password (password) - No name or id (select) - form (submit) This form is submitted by using the following action : https://juice-shop-388277804329.us-west1.run.app/login.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': 'form', 'input_name': 'combined:post::https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'payload': '', 'proof': '', 'output': 'A form with no identifier has been detected on the following URL https://juice-shop-388277804329.us-west1.run.app /user_new.php with input fields : - login (text) - email (text) - password (password) - password_conf (password) - secret (text) - mail_activation (checkbox) - action (submit) This form is submitted by using the following action : https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5789,15 +4068,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5826,31 +4101,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the presence of 24 URLs on the target application: - 0 URLs which use a hostname related to the target hostname - 24 URLs which use a third party hostname The list of the detected URLs is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5873,15 +4123,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5910,31 +4156,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/db/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/documents/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/js/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/info.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/images/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/login.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Permissions-Policy headers were found on https://juice-shop-388277804329.us-west1.run.app/training.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5957,15 +4178,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -5994,31 +4211,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords /wp-config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class. nusoap_base.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class. wsdlcache.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords /web.config.bak', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/db/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app /info_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/class. soap_fault.php', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app /training_install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/soap/nusoap. php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/passwords /heroes.xml', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/images/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/login.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/training.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/js/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/info.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/db/bwapp. sqlite', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/documents/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/apps/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/install.php', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/apps /movie_search', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'No Referrer-Policy headers or body meta tags were found on https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6041,15 +4233,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6078,31 +4266,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/robots.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "A robots.txt file was detected at 'https://juice-shop-388277804329.us-west1.run.app/robots.txt'.", 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/plain'}]</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6125,15 +4288,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6162,31 +4321,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Certificate 1 -------------- Common Name: *.a.run.app Alternative Names: *.a.run.app run.app *.africa-south1.run.app *.asia-east1.run.app *.asia-east2.run.app *.asia\ufffenortheast1.run.app *.asia-northeast2.run.app *.asia-northeast3.run.app *.asia-south1.run.app *.asia-south2.run.app *. asia-southeast1.run.app *.asia-southeast2.run.app *.australia-southeast1.run.app *.australia-southeast2.run.app *. europe-central2.run.app *.europe-north1.run.app *.europe-north2.run.app *.europe-southwest1.run.app *.europe-west1.run. app *.europe-west10.run.app *.europe-west12.run.app *.europe-west2.run.app *.europe-west3.run.app *.europe-west4.run. app *.europe-west5.run.app *.europe-west6.run.app *.europe-west8.run.app *.europe-west9.run.app *.me-central1.run.app *. me-central2.run.app *.me-west1.run.app *.northamerica-northeast1.run.app *.northamerica-northeast2.run.app *. northamerica-south1.run.app *.southamerica-east1.run.app *.southamerica-west1.run.app *.us-central1.run.app *.us\ufffecentral2.run.app *.us-east1.run.app *.us-east4.run.app *.us-east5.run.app *.us-east7.run.app *.us-south1.run.app *.us\ufffewest1.run.app *.us-west2.run.app *.us-west3.run.app *.us-west4.run.app *.us-west8.run.app Issuer: Google Trust Services Valid from: 2024-10-21 08:36:39 UTC Valid until: 2025-01-13 08:36:38 UTC (expires in 1 month, 3 weeks, 3 days) Validity Period: 83 days Key: RSA 256-bit Signature: sha256WithRSAEncryption Certificate 2 -------------- Common Name: wr Issuer: Google Trust Services LLC Valid from: 2023-12-13 09:00:00 UTC Valid until: 2029-02-20 14:00:00 UTC (expires in 4 years, 3 months, 2 days) Validity Period: 1896 days Key: RSA 2048-bit Signature: sha256WithRSAEncryption Certificate 3 -------------- Common Name: gts root r Issuer: GlobalSign nv Valid from: 2020-06-19 00:00:42 UTC Valid until: 2028-01-28 00:00:42 UTC (expires in 3 years, 2 months, 1 week, 1 day) Validity Period: 2779 days Key: RSA 4096-bit Signature: sha256WithRSAEncryption', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6209,15 +4343,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6246,31 +4376,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/documents/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.soap_fault.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': 'GET', 'http_status_code': 500, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.wsdlcache.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/images/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/wp-config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/web.config.bak', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'application/x-trash'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/stylesheets/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/js/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/nusoap.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/soap/class.nusoap_base.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/apps/movie_search', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/passwords/heroes.xml', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the lack of X-XSS-Protection header in the target application response.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6293,15 +4398,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6330,31 +4431,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Supported --------------------- SSL 2.0 No SSL 3.0 No TLS 1.0 No TLS 1.1 No TLS 1.2 Yes TLS 1.3 Yes', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6377,15 +4453,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6414,31 +4486,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected that the remote host is not configured with a cipher suite preference for the following protocol (s) : TLS v1.2, TLS v1.3', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6461,15 +4508,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6498,31 +4541,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'The scanner detected the following HTTP versions on the target application : - HTTP/1.0 - HTTP/1.1 - HTTP/2 The list of requests and responses observed is provided in attachment.', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6545,15 +4563,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6582,31 +4596,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': "No or a malformed security.txt was found at 'https://juice-shop-388277804329.us-west1.run.app/.well-known/security.txt'.", 'request_method': 'GET', 'http_status_code': 404, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6629,15 +4618,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6666,31 +4651,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'A wildcard symbol (*) has been detected in the following certificate entries: Certificate Common Name: *.a.run.app Certificate Subject Alternative Names: - *.a.run.app - *.africa-south1.run.app - *.asia-east1.run.app - *.asia-east2.run.app - *.asia-northeast1.run.app - *.asia-northeast2.run.app - *.asia-northeast3.run.app - *.asia-south1.run.app - *.asia-south2.run.app - *.asia-southeast1.run.app - *.asia-southeast2.run.app - *.australia-southeast1.run.app - *.australia-southeast2.run.app - *.europe-central2.run.app - *.europe-north1.run.app - *.europe-north2.run.app - *.europe-southwest1.run.app - *.europe-west1.run.app - *.europe-west10.run.app - *.europe-west12.run.app - *.europe-west2.run.app - *.europe-west3.run.app - *.europe-west4.run.app - *.europe-west5.run.app - *.europe-west6.run.app - *.europe-west8.run.app - *.europe-west9.run.app - *.me-central1.run.app - *.me-central2.run.app - *.me-west1.run.app - *.northamerica-northeast1.run.app - *.northamerica-northeast2.run.app - *.northamerica-south1.run.app - *.southamerica-east1.run.app - *.southamerica-west1.run.app - *.us-central1.run.app - *.us-central2.run.app - *.us-east1.run.app - *.us-east4.run.app - *.us-east5.run.app - *.us-east7.run.app - *.us-south1.run.app - *.us-west1.run.app - *.us-west2.run.app - *.us-west3.run.app - *.us-west4.run.app - *.us-west8.run.app', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6713,15 +4673,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6750,31 +4706,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Three attachments are included in this finding to assist in performance tuning of your scan: -pages_telemetry.csv: Scan statistics organized by page -plugins_telemetry.csv: Scan statistics organized by plugin -time_telemetry.csv: Chronological scan statistics', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6797,15 +4728,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6834,31 +4761,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php?install=yes', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/db/bwapp.sqlite', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': '2 HTML comments have been detected in the application HTTP response. Please see the attachment for further details.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6881,15 +4783,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -6918,31 +4816,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'cookie', 'input_name': 'PHPSESSID', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-User', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept-Charset', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Ch-Ua', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Ch-Ua-Platform', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept-Encoding', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-Mode', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'cookie', 'input_name': 'was-tnb-hsv', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Priority', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-Site', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Parameter name fuzzing', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Upgrade-Insecure-Requests', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Cookie', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept-Language', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Pragma', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Fetch-Dest', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Accept', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'User-Agent', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/phpinfo.php', 'input_type': 'header', 'input_name': 'Sec-Ch-Ua-Mobile', 'payload': 'was-tnb-hsv', 'proof': "Input reflected in the response body : 'was-tnb-hsv'.", 'output': 'The scanner was able to detect an input reflected in the response body.', 'request_method': 'GET', 'http_status_code': 200, 'http_protocol': 'HTTP/2', 'response_content_type': 'text/html'}]</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6965,15 +4838,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -7002,31 +4871,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/login.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php?install=yes', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training_install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/install.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/training.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/info.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}, {'instance': 'https://juice-shop-388277804329.us-west1.run.app/user_new.php', 'input_type': '', 'input_name': '', 'payload': '', 'proof': "The following value is extracted from a &lt;link&gt; tag that imports a style sheet with a 'href' that does not begin with a / : * stylesheets/stylesheet.css", 'output': 'The scanner was able to detect a Path Relative Stylesheet Import.', 'request_method': '', 'http_status_code': 200, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7049,15 +4893,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -7086,31 +4926,6 @@
           <t>[{'instance': 'https://juice-shop-388277804329.us-west1.run.app/#/', 'input_type': '', 'input_name': '', 'payload': '', 'proof': '', 'output': 'Protocol Cipher Suite Name (RFC) Key Exchange Strength ---------------------------------------------------------------------------- TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_CHACHA20_POLY1305 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_ECDSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_GCM_SHA256 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_GCM_SHA384 x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_128_CBC_SHA x25519 256 TLS1.2 TLS_ECDHE_RSA_WITH_AES_256_CBC_SHA x25519 256 TLS1.2 TLS_RSA_WITH_AES_128_GCM_SHA256 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_GCM_SHA384 RSA 4096 TLS1.2 TLS_RSA_WITH_AES_128_CBC_SHA RSA 4096 TLS1.2 TLS_RSA_WITH_AES_256_CBC_SHA RSA 4096 TLS1.3 TLS_AES_128_GCM_SHA256 x25519 256 TLS1.3 TLS_AES_256_GCM_SHA384 x25519 256 TLS1.3 TLS_CHACHA20_POLY1305_SHA256 x25519 256', 'request_method': '', 'http_status_code': None, 'http_protocol': '', 'response_content_type': ''}]</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/tenable/TenableWAS_bWAPP.xlsx
+++ b/resources/tenable/TenableWAS_bWAPP.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,6 +519,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -579,6 +582,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -639,6 +645,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -699,6 +708,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -759,6 +771,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -819,6 +834,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -879,6 +897,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -939,6 +960,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -999,6 +1023,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1059,6 +1086,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1119,6 +1149,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1179,6 +1212,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1239,6 +1275,9 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1299,6 +1338,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1359,6 +1401,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1419,6 +1464,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1479,6 +1527,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1539,6 +1590,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1599,6 +1653,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1659,6 +1716,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1719,6 +1779,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1779,6 +1842,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1839,6 +1905,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1899,6 +1968,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -1959,6 +2031,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2019,6 +2094,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2079,6 +2157,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2139,6 +2220,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2176,7 +2260,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['An information disclosure vulnerability exists in the remote web server due to the disclosure of the web.config file. An unauthenticated, remote attacker can exploit this, via a simple GET request, to disclose potentially sensitive configuration information.', 'The scanner detected the presence of the `web.config` file on https://juice-shop-388277804329.us-west1.run.app/passwords/web.config']</t>
+          <t>['An information disclosure vulnerability exists in the remote web server due to the disclosure of the web.config file. An unauthenticated, remote attacker can exploit this, via a simple GET request, to disclose potentially sensitive configuration information.']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2199,6 +2283,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2259,6 +2346,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2319,6 +2409,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2378,6 +2471,10 @@
           <t>['CWE 20', 'CWE 400', 'WASC Denial of Service', 'WASC Improper Input Handling', 'OWASP 2010-A4', 'OWASP 2021-A3', 'OWASP 2021-A6', 'OWASP 2013-A9', 'OWASP 2013-A4', 'OWASP 2017-A9', 'OWASP 2017-A5', 'OWASP 2019-API7', 'OWASP 2023-API8', 'CVE-2018-11763', 'BID 105414']</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2418,11 +2515,7 @@
           <t>['The HttpOnly flag assists in the prevention of client side-scripts (such as JavaScript) from accessing and using the cookie.', ""This can help prevent XSS attacks from targeting the cookies holding the client's session token (setting the HttpOnly flag does not prevent, nor safeguard against XSS vulnerabilities themselves).""]</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>['The initial step to remedy this would be to determine whether any client-side scripts (such as JavaScript) need to access the cookie and if not, set the HttpOnly flag.', 'It should be noted that some older browsers are not compatible with the HttpOnly flag; therefore, setting this flag will not protect those clients against this form of attack.']</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2438,6 +2531,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2479,11 +2575,7 @@
 to a malicious actor.']</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>['Restrict access to the web server file or remove it.']</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2499,6 +2591,9 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2565,6 +2660,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2630,6 +2728,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2694,6 +2795,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2754,6 +2858,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2814,6 +2921,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2874,6 +2984,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2934,6 +3047,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -2969,11 +3085,7 @@
           <t>Missing Content Security Policy</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>['Content Security Policy (CSP) is a web security standard that helps to mitigate attacks like cross-site scripting (XSS), clickjacking or mixed content issues. CSP provides mechanisms to websites to restrict content that browsers will be allowed to load. No CSP header has been detected on this host. This URL is flagged as a specific example.']</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>[""Configure Content Security Policy on your website by adding 'Content-Security-Policy' HTTP header or meta tag http-equiv='Content-Security-Policy'.""]</t>
@@ -2994,6 +3106,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3054,6 +3169,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3114,6 +3232,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3174,6 +3295,9 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3224,11 +3348,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3298,11 +3426,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3353,11 +3485,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3408,11 +3544,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3463,11 +3603,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3518,11 +3662,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3573,11 +3721,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3628,11 +3780,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3683,11 +3839,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3738,11 +3898,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3793,11 +3957,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3848,11 +4016,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3888,11 +4060,7 @@
           <t>Target Information</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>['Publishes the target information of the starting url as evaluated by the scan.']</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>['-']</t>
@@ -3903,11 +4071,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3958,11 +4130,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -3998,11 +4174,7 @@
           <t>Form Detected</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>['The scanner has detected the presence of a form during the crawling of the target web application. Details about the form are provided in the plugin output.']</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>['-']</t>
@@ -4013,11 +4185,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4068,11 +4244,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4123,11 +4303,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4178,11 +4362,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4233,11 +4421,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4288,11 +4480,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4343,11 +4539,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4398,11 +4598,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4453,11 +4657,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4508,11 +4716,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4563,11 +4775,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4618,11 +4834,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4673,11 +4893,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4728,11 +4952,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4783,11 +5011,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4838,11 +5070,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
@@ -4878,11 +5114,7 @@
           <t>SSL/TLS Cipher Suites Supported</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>['This plugin displays supported SSL/TLS cipher suites.']</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>['-']</t>
@@ -4893,11 +5125,15 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>TENABLEWAS</t>
